--- a/outputs/daily/hr_rankings_2026-08-23_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-23_remaining.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>63.1</v>
+        <v>63.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>40.1</v>
       </c>
       <c r="R2" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -826,34 +826,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1003,7 +999,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1068,11 +1064,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>60.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1082,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1092,10 +1088,10 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1105,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1287,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1308,7 +1300,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1333,7 +1325,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1352,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.3</v>
+        <v>58.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1366,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1376,10 +1368,10 @@
         <v>35.9</v>
       </c>
       <c r="R4" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
@@ -1389,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -1571,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1587,24 +1575,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>686948</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -1617,26 +1605,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.8</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1650,65 +1638,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>56.7</v>
+        <v>51.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>35.9</v>
+        <v>40.1</v>
       </c>
       <c r="R5" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>28.1</v>
+        <v>32</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1725,7 +1709,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1735,17 +1719,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1755,97 +1739,97 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>91.12</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.3923</t>
+          <t>101.9311</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4933</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2164</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.3308</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.23</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>55.25</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>0.1881</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.55</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.4074</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -1855,7 +1839,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1871,24 +1855,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>686948</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -1901,26 +1885,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1934,26 +1918,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>51.5</v>
+        <v>56.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>40.1</v>
+        <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>32</v>
+        <v>28.1</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1962,37 +1946,33 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -2009,7 +1989,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2019,17 +1999,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2039,97 +2019,97 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.12</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.9311</t>
+          <t>102.3923</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4933</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.2164</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3308</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>75.23</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>55.25</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1881</t>
+          <t>0.181</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.55</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4074</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -2139,7 +2119,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2155,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -2185,26 +2165,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.5</v>
+        <v>53.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2218,26 +2198,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.4</v>
+        <v>46.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>40.1</v>
+        <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>61.4</v>
+        <v>40.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2246,37 +2226,33 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2298,22 +2274,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Contact streak: 11/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2323,97 +2299,97 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>10.36</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>101.6343</t>
+          <t>103.3725</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4259</t>
+          <t>0.4674</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3336</t>
+          <t>0.336</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>35.46</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>36.32</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>21.93</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1285</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>89.55</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.4074</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -2423,7 +2399,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2439,12 +2415,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2469,7 +2445,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2488,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.3</v>
+        <v>53.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2502,26 +2478,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>37</v>
+        <v>38.4</v>
       </c>
       <c r="Q8" t="n">
         <v>40.1</v>
       </c>
       <c r="R8" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>2.7</v>
+        <v>61.4</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2530,34 +2506,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2577,27 +2549,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/29, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2607,67 +2579,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.4233</t>
+          <t>101.6343</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.4259</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1719</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3399</t>
+          <t>0.3336</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.18</t>
+          <t>73.34</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>35.46</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>36.32</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.08</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1659</t>
+          <t>0.1285</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2707,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2723,12 +2695,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2753,7 +2725,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2772,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.2</v>
+        <v>52.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2786,26 +2758,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>47.7</v>
+        <v>37</v>
       </c>
       <c r="Q9" t="n">
         <v>40.1</v>
       </c>
       <c r="R9" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>63.3</v>
+        <v>2.7</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2814,34 +2786,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2861,22 +2829,22 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 4/29, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2886,72 +2854,72 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>43.69</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>92.15</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>103.6934</t>
+          <t>100.4233</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4117</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1719</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.3399</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>70.18</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>17.83</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1384</t>
+          <t>0.1659</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2991,7 +2959,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3007,12 +2975,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3037,7 +3005,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -3056,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51</v>
+        <v>52.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3074,22 +3042,22 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.2</v>
+        <v>47.7</v>
       </c>
       <c r="Q10" t="n">
         <v>40.1</v>
       </c>
       <c r="R10" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>28.1</v>
+        <v>63.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3098,34 +3066,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3145,12 +3109,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3160,7 +3124,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -3170,72 +3134,72 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.36</t>
+          <t>92.15</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.0352</t>
+          <t>103.6934</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4033</t>
+          <t>0.4117</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.09</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1551</t>
+          <t>0.1384</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -3275,7 +3239,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3291,24 +3255,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -3321,26 +3285,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49.8</v>
+        <v>51.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3354,65 +3318,61 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>53.7</v>
+        <v>39.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>35.9</v>
+        <v>40.1</v>
       </c>
       <c r="R11" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>10.8</v>
+        <v>28.1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3434,22 +3394,22 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3459,97 +3419,97 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>89.36</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>102.9742</t>
+          <t>101.0352</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4181</t>
+          <t>0.4033</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1963</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>75.76</t>
+          <t>73.09</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1512</t>
+          <t>0.1551</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.55</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.4074</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -3559,7 +3519,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3575,12 +3535,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3605,7 +3565,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3624,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.7</v>
+        <v>50.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3638,62 +3598,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>46.4</v>
+        <v>53.7</v>
       </c>
       <c r="Q12" t="n">
         <v>35.9</v>
       </c>
       <c r="R12" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>40.9</v>
+        <v>10.8</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -3713,12 +3669,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3728,12 +3684,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/28 over last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3743,67 +3699,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>103.3725</t>
+          <t>102.9742</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4674</t>
+          <t>0.4181</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.1963</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>75.76</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.1512</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -3843,7 +3799,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -3908,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3932,7 +3888,7 @@
         <v>40.1</v>
       </c>
       <c r="R13" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -3950,34 +3906,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4127,7 +4079,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4173,7 +4125,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -4192,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.7</v>
+        <v>46.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4206,7 +4158,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4216,10 +4168,10 @@
         <v>35.9</v>
       </c>
       <c r="R14" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>78</v>
@@ -4229,39 +4181,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4411,7 +4359,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4476,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>43.4</v>
+        <v>44.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4490,7 +4438,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -4500,10 +4448,10 @@
         <v>35</v>
       </c>
       <c r="R15" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -4513,39 +4461,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4695,7 +4639,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4760,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4784,7 +4728,7 @@
         <v>40.1</v>
       </c>
       <c r="R16" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -4800,28 +4744,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4971,7 +4919,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -4992,7 +4940,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5036,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>38.5</v>
+        <v>39.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5050,7 +4998,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -5060,10 +5008,10 @@
         <v>35.9</v>
       </c>
       <c r="R17" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>78</v>
@@ -5073,39 +5021,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5255,7 +5199,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -5320,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5344,7 +5288,7 @@
         <v>40.1</v>
       </c>
       <c r="R18" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -5362,34 +5306,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5539,7 +5479,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5604,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>34.6</v>
+        <v>35.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5618,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5628,10 +5568,10 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>78</v>
@@ -5641,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5823,7 +5759,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6214,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>63.1</v>
+        <v>63.6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6238,7 +6174,7 @@
         <v>40.1</v>
       </c>
       <c r="R2" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -6256,34 +6192,30 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6433,7 +6365,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -6498,11 +6430,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>59</v>
+        <v>60.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Longshot</t>
+          <t>Tier 3</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -6512,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6522,10 +6454,10 @@
         <v>35.9</v>
       </c>
       <c r="R3" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -6535,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -6717,7 +6645,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -6738,7 +6666,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6763,7 +6691,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6782,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>56.3</v>
+        <v>58.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6796,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6806,10 +6734,10 @@
         <v>35.9</v>
       </c>
       <c r="R4" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
@@ -6819,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7001,7 +6925,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -7017,24 +6941,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>686948</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -7047,26 +6971,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.8</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7080,65 +7004,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>56.7</v>
+        <v>51.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>35.9</v>
+        <v>40.1</v>
       </c>
       <c r="R5" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
       </c>
       <c r="U5" t="n">
-        <v>28.1</v>
+        <v>32</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -7155,7 +7075,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -7165,17 +7085,17 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -7185,97 +7105,97 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>12.47</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>51.28</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>91.12</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>102.3923</t>
+          <t>101.9311</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4933</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2164</t>
+          <t>0.2063</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.3308</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.23</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>55.25</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>32.64</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20.4</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>0.1881</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.55</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.4074</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
@@ -7285,7 +7205,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -7301,24 +7221,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>686948</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -7331,26 +7251,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7364,26 +7284,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>51.5</v>
+        <v>56.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>40.1</v>
+        <v>35.9</v>
       </c>
       <c r="R6" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>32</v>
+        <v>28.1</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -7392,37 +7312,33 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -7439,7 +7355,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -7449,17 +7365,17 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7469,97 +7385,97 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.47</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>51.28</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.12</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.9311</t>
+          <t>102.3923</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4933</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2063</t>
+          <t>0.2164</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3308</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>75.23</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>55.25</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>32.64</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1881</t>
+          <t>0.181</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.55</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4074</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -7569,7 +7485,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -7585,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -7615,26 +7531,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Shane Drohan</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>675660</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>52.5</v>
+        <v>53.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7648,26 +7564,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.4</v>
+        <v>46.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>40.1</v>
+        <v>35.9</v>
       </c>
       <c r="R7" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T7" t="n">
         <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>61.4</v>
+        <v>40.9</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -7676,37 +7592,33 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -7728,22 +7640,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Contact streak: 11/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7753,97 +7665,97 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>10.36</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>47.25</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>101.6343</t>
+          <t>103.3725</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4259</t>
+          <t>0.4674</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3336</t>
+          <t>0.336</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.34</t>
+          <t>74.79</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>35.46</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>36.32</t>
+          <t>36.29</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>21.93</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1285</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.65</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>37.59</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>89.55</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.4074</t>
+          <t>0.367</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1579</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>28.59</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -7853,7 +7765,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -7869,12 +7781,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7899,7 +7811,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7918,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>52.3</v>
+        <v>53.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7932,26 +7844,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>37</v>
+        <v>38.4</v>
       </c>
       <c r="Q8" t="n">
         <v>40.1</v>
       </c>
       <c r="R8" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>2.7</v>
+        <v>61.4</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -7960,34 +7872,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8007,27 +7915,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/29, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -8037,67 +7945,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>90.61</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.4233</t>
+          <t>101.6343</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4297</t>
+          <t>0.4259</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1719</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3399</t>
+          <t>0.3336</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.18</t>
+          <t>73.34</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>35.46</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>36.32</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>24.13</t>
+          <t>24.08</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1659</t>
+          <t>0.1285</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -8137,7 +8045,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -8153,12 +8061,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8183,7 +8091,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8202,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>52.2</v>
+        <v>52.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8216,26 +8124,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>47.7</v>
+        <v>37</v>
       </c>
       <c r="Q9" t="n">
         <v>40.1</v>
       </c>
       <c r="R9" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>63.3</v>
+        <v>2.7</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -8244,34 +8152,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8291,22 +8195,22 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 4/29, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -8316,72 +8220,72 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>43.69</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>92.15</t>
+          <t>90.61</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>103.6934</t>
+          <t>100.4233</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4117</t>
+          <t>0.4297</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1719</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.3399</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>77.08</t>
+          <t>70.18</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>17.83</t>
+          <t>24.13</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1384</t>
+          <t>0.1659</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -8421,7 +8325,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -8437,12 +8341,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8467,7 +8371,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8486,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51</v>
+        <v>52.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8504,22 +8408,22 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>39.2</v>
+        <v>47.7</v>
       </c>
       <c r="Q10" t="n">
         <v>40.1</v>
       </c>
       <c r="R10" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>28.1</v>
+        <v>63.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -8528,34 +8432,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8575,12 +8475,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -8590,7 +8490,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -8600,72 +8500,72 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.23</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>48.85</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>89.36</t>
+          <t>92.15</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.0352</t>
+          <t>103.6934</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4033</t>
+          <t>0.4117</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1681</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3167</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>73.09</t>
+          <t>77.08</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>19.16</t>
+          <t>17.83</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1551</t>
+          <t>0.1384</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -8705,7 +8605,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -8721,24 +8621,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-23T23:10:00Z</t>
@@ -8751,26 +8651,26 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shane Drohan</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>675660</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>49.8</v>
+        <v>51.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8784,65 +8684,61 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>53.7</v>
+        <v>39.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>35.9</v>
+        <v>40.1</v>
       </c>
       <c r="R11" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>10.8</v>
+        <v>28.1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -8864,22 +8760,22 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 5/27, 1 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8889,97 +8785,97 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>44.51</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>89.36</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>102.9742</t>
+          <t>101.0352</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4181</t>
+          <t>0.4033</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1963</t>
+          <t>0.1681</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.3167</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>75.76</t>
+          <t>73.09</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>19.16</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1512</t>
+          <t>0.1551</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.59</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.55</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>0.4074</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>0.1579</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.59</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -8989,7 +8885,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -9005,12 +8901,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -9035,7 +8931,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -9054,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.7</v>
+        <v>50.9</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9068,62 +8964,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>46.4</v>
+        <v>53.7</v>
       </c>
       <c r="Q12" t="n">
         <v>35.9</v>
       </c>
       <c r="R12" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>40.9</v>
+        <v>10.8</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9143,12 +9035,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -9158,12 +9050,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/28 over last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -9173,67 +9065,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.36</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>47.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>103.3725</t>
+          <t>102.9742</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4674</t>
+          <t>0.4181</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.1963</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>74.79</t>
+          <t>75.76</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>36.29</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21.93</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.1512</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -9273,7 +9165,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -9338,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>48.6</v>
+        <v>49.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9362,7 +9254,7 @@
         <v>40.1</v>
       </c>
       <c r="R13" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>86.40000000000001</v>
@@ -9380,34 +9272,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9557,7 +9445,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -9603,7 +9491,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -9622,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>46.7</v>
+        <v>46.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9636,7 +9524,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9646,10 +9534,10 @@
         <v>35.9</v>
       </c>
       <c r="R14" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>78</v>
@@ -9659,39 +9547,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9841,7 +9725,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -9906,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>43.4</v>
+        <v>44.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9920,7 +9804,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -9930,10 +9814,10 @@
         <v>35</v>
       </c>
       <c r="R15" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
@@ -9943,39 +9827,35 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10125,7 +10005,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -10190,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10214,7 +10094,7 @@
         <v>40.1</v>
       </c>
       <c r="R16" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -10230,28 +10110,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10401,7 +10285,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -10422,7 +10306,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10466,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>38.5</v>
+        <v>39.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10480,7 +10364,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10490,10 +10374,10 @@
         <v>35.9</v>
       </c>
       <c r="R17" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>78</v>
@@ -10503,39 +10387,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10685,7 +10565,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -10750,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>39</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10774,7 +10654,7 @@
         <v>40.1</v>
       </c>
       <c r="R18" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -10792,34 +10672,30 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10969,7 +10845,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -11034,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>34.6</v>
+        <v>35.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -11048,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -11058,10 +10934,10 @@
         <v>35.9</v>
       </c>
       <c r="R19" t="n">
-        <v>61.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>78</v>
@@ -11071,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11253,7 +11125,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
